--- a/Dados/Processado/PIB mesos long.xlsx
+++ b/Dados/Processado/PIB mesos long.xlsx
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>116874219330.4287</v>
+        <v>114991451000</v>
       </c>
     </row>
     <row r="53">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>124669407488.401</v>
+        <v>122576918236.4019</v>
       </c>
     </row>
     <row r="54">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>128658497292.7534</v>
+        <v>126439673448.2582</v>
       </c>
     </row>
     <row r="55">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>130946475692.6546</v>
+        <v>128640304883.7807</v>
       </c>
     </row>
     <row r="56">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>135816984725.8449</v>
+        <v>133350782716.4825</v>
       </c>
     </row>
     <row r="57">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>141700467909.8108</v>
+        <v>139039234660.661</v>
       </c>
     </row>
     <row r="58">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>147517584346.5835</v>
+        <v>144655418604.4932</v>
       </c>
     </row>
     <row r="59">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>153464871902.6181</v>
+        <v>150391143565.1407</v>
       </c>
     </row>
     <row r="60">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>527187560295.2091</v>
+        <v>513392972000</v>
       </c>
     </row>
     <row r="111">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>558906394419.1664</v>
+        <v>543501951353.0205</v>
       </c>
     </row>
     <row r="112">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>576597286126.8094</v>
+        <v>560087449245.321</v>
       </c>
     </row>
     <row r="113">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>587827429378.0125</v>
+        <v>570412871430.1521</v>
       </c>
     </row>
     <row r="114">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>608602144157.7544</v>
+        <v>589808586340.6432</v>
       </c>
     </row>
     <row r="115">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>633109280042.0946</v>
+        <v>612688589683.0004</v>
       </c>
     </row>
     <row r="116">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>657181391824.7495</v>
+        <v>635056642116.1494</v>
       </c>
     </row>
     <row r="117">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>681473804086.1945</v>
+        <v>657533287733.8291</v>
       </c>
     </row>
     <row r="118">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>58679646215.23186</v>
+        <v>58666946745.58228</v>
       </c>
     </row>
     <row r="170">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>59973562615.98818</v>
+        <v>59952209180.83891</v>
       </c>
     </row>
     <row r="171">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>60837654475.17936</v>
+        <v>60809516138.87469</v>
       </c>
     </row>
     <row r="172">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>62289561271.09489</v>
+        <v>62250591963.8491</v>
       </c>
     </row>
     <row r="173">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>63945087976.8852</v>
+        <v>63893197248.35519</v>
       </c>
     </row>
     <row r="174">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>65540229652.35498</v>
+        <v>65474841377.2045</v>
       </c>
     </row>
     <row r="175">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>67115240061.29616</v>
+        <v>67035510133.50847</v>
       </c>
     </row>
     <row r="176">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>167787492964.7804</v>
+        <v>155875673000</v>
       </c>
     </row>
     <row r="198">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>181854177759.9636</v>
+        <v>168554923415.4665</v>
       </c>
     </row>
     <row r="199">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>190370555101.6988</v>
+        <v>176100895499.8551</v>
       </c>
     </row>
     <row r="200">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>196247096206.7178</v>
+        <v>181166847404.0359</v>
       </c>
     </row>
     <row r="201">
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>206277210175.0201</v>
+        <v>189988823674.5169</v>
       </c>
     </row>
     <row r="202">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>218082799060.4831</v>
+        <v>200375232679.0689</v>
       </c>
     </row>
     <row r="203">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>229857836546.2732</v>
+        <v>210660640854.914</v>
       </c>
     </row>
     <row r="204">
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>241867082203.6446</v>
+        <v>221080024116.5443</v>
       </c>
     </row>
   </sheetData>
